--- a/data/trans_orig/P36B13_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P36B13_R-Edad-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>93768</t>
+          <t>93359</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>131431</t>
+          <t>131317</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>22,26%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>31,33%</t>
+          <t>31,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>65719</t>
+          <t>65259</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>97360</t>
+          <t>96296</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>24,39%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>169671</t>
+          <t>172251</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>217874</t>
+          <t>220897</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>27,13%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>288032</t>
+          <t>288146</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>325695</t>
+          <t>326104</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>68,67%</t>
+          <t>68,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>77,65%</t>
+          <t>77,74%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>297422</t>
+          <t>298486</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>329063</t>
+          <t>329523</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>75,34%</t>
+          <t>75,61%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>83,35%</t>
+          <t>83,47%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>596371</t>
+          <t>593348</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>644574</t>
+          <t>641994</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>73,24%</t>
+          <t>72,87%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>79,16%</t>
+          <t>78,85%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>111071</t>
+          <t>110441</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>150647</t>
+          <t>151480</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,12 +1089,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,55%</t>
+          <t>25,69%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>52568</t>
+          <t>53462</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>82500</t>
+          <t>82357</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,12 +1124,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>174729</t>
+          <t>172201</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>226437</t>
+          <t>224701</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>19,5%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>438951</t>
+          <t>438118</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>478527</t>
+          <t>479157</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,12 +1202,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>74,45%</t>
+          <t>74,31%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>81,16%</t>
+          <t>81,27%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>480163</t>
+          <t>480306</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>510095</t>
+          <t>509201</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,34%</t>
+          <t>85,36%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,66%</t>
+          <t>90,5%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>925824</t>
+          <t>927560</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>977532</t>
+          <t>980060</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>80,35%</t>
+          <t>80,5%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>84,84%</t>
+          <t>85,06%</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>62751</t>
+          <t>64086</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>96499</t>
+          <t>97697</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>40258</t>
+          <t>41112</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>68874</t>
+          <t>68383</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1467,12 +1467,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>111213</t>
+          <t>109479</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>155063</t>
+          <t>154787</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,12 +1502,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,69%</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>568900</t>
+          <t>567702</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>602648</t>
+          <t>601313</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,12 +1545,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>85,5%</t>
+          <t>85,32%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,57%</t>
+          <t>90,37%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>589595</t>
+          <t>590086</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>618211</t>
+          <t>617357</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,12 +1580,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,54%</t>
+          <t>89,61%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,89%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1168805</t>
+          <t>1169081</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1212655</t>
+          <t>1214389</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,29%</t>
+          <t>88,31%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,6%</t>
+          <t>91,73%</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>36429</t>
+          <t>38369</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>65372</t>
+          <t>65963</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>22607</t>
+          <t>23570</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>45588</t>
+          <t>44736</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,12 +1810,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>66313</t>
+          <t>67213</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>103011</t>
+          <t>102160</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>7,92%</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>579551</t>
+          <t>578960</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>608494</t>
+          <t>606554</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,86%</t>
+          <t>89,77%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>94,05%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>600185</t>
+          <t>601037</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>623166</t>
+          <t>622203</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,12 +1923,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>93,07%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1187685</t>
+          <t>1188536</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1224383</t>
+          <t>1223483</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,02%</t>
+          <t>92,08%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>94,79%</t>
         </is>
       </c>
     </row>
@@ -2103,12 +2103,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>16116</t>
+          <t>16219</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>36471</t>
+          <t>36541</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2118,12 +2118,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>14188</t>
+          <t>14207</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>34388</t>
+          <t>33893</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2153,12 +2153,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>34271</t>
+          <t>34429</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>63585</t>
+          <t>61918</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2188,12 +2188,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,41%</t>
         </is>
       </c>
     </row>
@@ -2216,12 +2216,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>433921</t>
+          <t>433851</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>454276</t>
+          <t>454173</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2231,12 +2231,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,25%</t>
+          <t>92,23%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>461217</t>
+          <t>461712</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>481417</t>
+          <t>481398</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2266,12 +2266,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,06%</t>
+          <t>93,16%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>902412</t>
+          <t>904079</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>931726</t>
+          <t>931568</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2301,12 +2301,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,42%</t>
+          <t>93,59%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,44%</t>
         </is>
       </c>
     </row>
@@ -2446,12 +2446,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6615</t>
+          <t>6891</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>20413</t>
+          <t>20062</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2461,12 +2461,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2481,12 +2481,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6202</t>
+          <t>6082</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>19770</t>
+          <t>19149</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2516,12 +2516,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>15724</t>
+          <t>16007</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>34600</t>
+          <t>35928</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>5,07%</t>
         </is>
       </c>
     </row>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>311920</t>
+          <t>312271</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>325718</t>
+          <t>325442</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2574,12 +2574,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>93,96%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2594,12 +2594,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>355977</t>
+          <t>356598</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>369545</t>
+          <t>369665</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2609,12 +2609,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,9%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2629,12 +2629,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>673480</t>
+          <t>672152</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>692356</t>
+          <t>692073</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2644,12 +2644,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>94,93%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,74%</t>
         </is>
       </c>
     </row>
@@ -2789,12 +2789,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4414</t>
+          <t>4703</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>16204</t>
+          <t>16516</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2804,12 +2804,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3799</t>
+          <t>3919</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>17674</t>
+          <t>18029</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2839,47 +2839,47 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
+          <t>4,65%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>17812</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>11100</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>29130</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>2,78%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>1,74%</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
           <t>4,55%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>17812</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>10505</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>27406</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>2,78%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>1,64%</t>
-        </is>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t>4,28%</t>
         </is>
       </c>
     </row>
@@ -2902,12 +2902,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>235453</t>
+          <t>235141</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>247243</t>
+          <t>246954</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2917,12 +2917,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,56%</t>
+          <t>93,44%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2937,12 +2937,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>370432</t>
+          <t>370077</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>384307</t>
+          <t>384187</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2952,47 +2952,47 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
+          <t>95,35%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>98,99%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>573</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>621951</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>610633</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>628663</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>97,22%</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
           <t>95,45%</t>
         </is>
       </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>99,02%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>573</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>621951</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>612357</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>629258</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>97,22%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>95,72%</t>
-        </is>
-      </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,26%</t>
         </is>
       </c>
     </row>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>383818</t>
+          <t>385296</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>460533</t>
+          <t>460979</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3147,12 +3147,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>247534</t>
+          <t>246674</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>310290</t>
+          <t>307483</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3182,12 +3182,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>651834</t>
+          <t>647309</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>748461</t>
+          <t>745995</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3217,12 +3217,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>10,82%</t>
         </is>
       </c>
     </row>
@@ -3245,12 +3245,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2913232</t>
+          <t>2912786</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2989947</t>
+          <t>2988469</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3260,12 +3260,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>86,35%</t>
+          <t>86,34%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>88,62%</t>
+          <t>88,58%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3210856</t>
+          <t>3213663</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3273612</t>
+          <t>3274472</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3295,12 +3295,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>91,19%</t>
+          <t>91,27%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>92,99%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6146450</t>
+          <t>6148916</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6243077</t>
+          <t>6247602</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>89,14%</t>
+          <t>89,18%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>90,55%</t>
+          <t>90,61%</t>
         </is>
       </c>
     </row>
@@ -3705,32 +3705,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>51100</t>
+          <t>53376</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>32726</t>
+          <t>35289</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>78687</t>
+          <t>78203</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>19,18%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3740,32 +3740,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>33629</t>
+          <t>40791</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>21654</t>
+          <t>27504</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>49532</t>
+          <t>60441</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3775,32 +3775,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>84729</t>
+          <t>94168</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>60805</t>
+          <t>70026</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>112770</t>
+          <t>126203</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>16,42%</t>
         </is>
       </c>
     </row>
@@ -3818,32 +3818,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>348887</t>
+          <t>354417</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>321300</t>
+          <t>329590</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>367261</t>
+          <t>372504</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>87,22%</t>
+          <t>86,91%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>80,33%</t>
+          <t>80,82%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>91,35%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3853,32 +3853,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>277988</t>
+          <t>320224</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>262085</t>
+          <t>300574</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>289963</t>
+          <t>333511</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>89,21%</t>
+          <t>88,7%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,1%</t>
+          <t>83,26%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,05%</t>
+          <t>92,38%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3888,32 +3888,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>626875</t>
+          <t>674641</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>598834</t>
+          <t>642606</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>650799</t>
+          <t>698783</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>88,09%</t>
+          <t>87,75%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>84,15%</t>
+          <t>83,58%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,46%</t>
+          <t>90,89%</t>
         </is>
       </c>
     </row>
@@ -3931,17 +3931,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3966,17 +3966,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>311617</t>
+          <t>361015</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>311617</t>
+          <t>361015</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>311617</t>
+          <t>361015</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4001,17 +4001,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>711604</t>
+          <t>768809</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>711604</t>
+          <t>768809</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>711604</t>
+          <t>768809</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4048,32 +4048,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>60017</t>
+          <t>68875</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>42018</t>
+          <t>50113</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>80646</t>
+          <t>91784</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4083,32 +4083,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>17131</t>
+          <t>17522</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8328</t>
+          <t>9985</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>28507</t>
+          <t>29164</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4118,32 +4118,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>77148</t>
+          <t>86398</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>53496</t>
+          <t>64377</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>102448</t>
+          <t>111266</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>11,38%</t>
         </is>
       </c>
     </row>
@@ -4161,32 +4161,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>363530</t>
+          <t>408015</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>342901</t>
+          <t>385106</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>381529</t>
+          <t>426777</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>85,83%</t>
+          <t>85,56%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>80,96%</t>
+          <t>80,75%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,08%</t>
+          <t>89,49%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4196,32 +4196,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>494373</t>
+          <t>483561</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>482997</t>
+          <t>471919</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>503176</t>
+          <t>491098</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>94,18%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4231,32 +4231,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>857903</t>
+          <t>891575</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>832603</t>
+          <t>866707</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>881555</t>
+          <t>913596</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>91,75%</t>
+          <t>91,17%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,04%</t>
+          <t>88,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>93,42%</t>
         </is>
       </c>
     </row>
@@ -4274,17 +4274,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4309,17 +4309,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4344,17 +4344,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4391,32 +4391,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>41336</t>
+          <t>46407</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>30221</t>
+          <t>34385</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>55572</t>
+          <t>61483</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4426,32 +4426,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>28167</t>
+          <t>33203</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>20422</t>
+          <t>24485</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>37264</t>
+          <t>43791</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4461,32 +4461,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>69503</t>
+          <t>79610</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>55439</t>
+          <t>64109</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>87505</t>
+          <t>99141</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>7,99%</t>
         </is>
       </c>
     </row>
@@ -4504,32 +4504,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>495002</t>
+          <t>574430</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>480766</t>
+          <t>559354</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>506117</t>
+          <t>586452</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>92,29%</t>
+          <t>92,53%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,64%</t>
+          <t>90,1%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4539,32 +4539,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>512647</t>
+          <t>587265</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>503550</t>
+          <t>576677</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>520392</t>
+          <t>595983</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>94,65%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,11%</t>
+          <t>92,94%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4574,32 +4574,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1007650</t>
+          <t>1161695</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>989648</t>
+          <t>1142164</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1021714</t>
+          <t>1177196</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>93,59%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>92,01%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>94,84%</t>
         </is>
       </c>
     </row>
@@ -4617,17 +4617,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4652,17 +4652,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>540814</t>
+          <t>620468</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>540814</t>
+          <t>620468</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>540814</t>
+          <t>620468</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4687,17 +4687,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1077153</t>
+          <t>1241305</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1077153</t>
+          <t>1241305</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1077153</t>
+          <t>1241305</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4734,32 +4734,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>284819</t>
+          <t>49032</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>49788</t>
+          <t>36416</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>632159</t>
+          <t>66665</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>32,15%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>71,36%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4769,32 +4769,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>24909</t>
+          <t>27388</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17742</t>
+          <t>19524</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>33210</t>
+          <t>36156</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4804,32 +4804,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>309728</t>
+          <t>76420</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>70955</t>
+          <t>62810</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>793302</t>
+          <t>94866</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>49,74%</t>
+          <t>6,63%</t>
         </is>
       </c>
     </row>
@@ -4847,32 +4847,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>601090</t>
+          <t>649785</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>253750</t>
+          <t>632152</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>836121</t>
+          <t>662401</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>67,85%</t>
+          <t>92,98%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>28,64%</t>
+          <t>90,46%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>94,79%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4882,32 +4882,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>684195</t>
+          <t>705686</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>675894</t>
+          <t>696918</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>691362</t>
+          <t>713550</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,07%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4917,32 +4917,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1285285</t>
+          <t>1355471</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>801711</t>
+          <t>1337025</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1524058</t>
+          <t>1369081</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>80,58%</t>
+          <t>94,66%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>50,26%</t>
+          <t>93,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,61%</t>
         </is>
       </c>
     </row>
@@ -4960,17 +4960,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>885909</t>
+          <t>698817</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>885909</t>
+          <t>698817</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>885909</t>
+          <t>698817</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -4995,17 +4995,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>709104</t>
+          <t>733074</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>709104</t>
+          <t>733074</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>709104</t>
+          <t>733074</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5030,17 +5030,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1595013</t>
+          <t>1431891</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1595013</t>
+          <t>1431891</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1595013</t>
+          <t>1431891</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5077,32 +5077,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>23022</t>
+          <t>27452</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>15115</t>
+          <t>18548</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>33158</t>
+          <t>38836</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5112,32 +5112,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>8809</t>
+          <t>9650</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5297</t>
+          <t>5571</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>14224</t>
+          <t>16559</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5147,32 +5147,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>31832</t>
+          <t>37102</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>22935</t>
+          <t>26969</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>43648</t>
+          <t>50450</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,15%</t>
         </is>
       </c>
     </row>
@@ -5190,32 +5190,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>536491</t>
+          <t>580172</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>526355</t>
+          <t>568788</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>544398</t>
+          <t>589076</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>95,48%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
+          <t>93,61%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5225,32 +5225,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>537076</t>
+          <t>597172</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>531661</t>
+          <t>590263</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>540588</t>
+          <t>601251</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5260,32 +5260,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1073566</t>
+          <t>1177345</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1061750</t>
+          <t>1163997</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1082463</t>
+          <t>1187478</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>96,94%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,78%</t>
         </is>
       </c>
     </row>
@@ -5303,17 +5303,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>559513</t>
+          <t>607624</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>559513</t>
+          <t>607624</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>559513</t>
+          <t>607624</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5338,17 +5338,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>545885</t>
+          <t>606822</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>545885</t>
+          <t>606822</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>545885</t>
+          <t>606822</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5373,17 +5373,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1105398</t>
+          <t>1214447</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1105398</t>
+          <t>1214447</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1105398</t>
+          <t>1214447</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5420,32 +5420,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>12409</t>
+          <t>13549</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7932</t>
+          <t>8476</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>19169</t>
+          <t>20755</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5455,32 +5455,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>5536</t>
+          <t>6501</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1685</t>
+          <t>3521</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10948</t>
+          <t>11529</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5490,32 +5490,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>17944</t>
+          <t>20050</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>9688</t>
+          <t>13557</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>27015</t>
+          <t>28698</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>3,39%</t>
         </is>
       </c>
     </row>
@@ -5533,32 +5533,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>355756</t>
+          <t>393531</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>348996</t>
+          <t>386325</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>360233</t>
+          <t>398604</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>94,9%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5568,32 +5568,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>602832</t>
+          <t>432665</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>597420</t>
+          <t>427637</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>606683</t>
+          <t>435645</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5603,32 +5603,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>958589</t>
+          <t>826196</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>949518</t>
+          <t>817548</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>966845</t>
+          <t>832689</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>98,4%</t>
         </is>
       </c>
     </row>
@@ -5646,17 +5646,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5681,17 +5681,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5716,17 +5716,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5763,32 +5763,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>4557</t>
+          <t>5086</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2171</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>9207</t>
+          <t>10374</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5798,32 +5798,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>8137</t>
+          <t>9321</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4789</t>
+          <t>5439</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>13796</t>
+          <t>16023</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5833,32 +5833,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>12695</t>
+          <t>14406</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>8000</t>
+          <t>9442</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>19301</t>
+          <t>22986</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,97%</t>
         </is>
       </c>
     </row>
@@ -5876,32 +5876,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>277654</t>
+          <t>304553</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>273004</t>
+          <t>299265</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>280190</t>
+          <t>307468</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5911,32 +5911,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>417104</t>
+          <t>454610</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>411445</t>
+          <t>447908</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>420452</t>
+          <t>458492</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5946,32 +5946,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>694757</t>
+          <t>759163</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>688151</t>
+          <t>750583</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>699452</t>
+          <t>764127</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,78%</t>
         </is>
       </c>
     </row>
@@ -5989,17 +5989,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>282211</t>
+          <t>309639</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>282211</t>
+          <t>309639</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>282211</t>
+          <t>309639</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6024,17 +6024,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>425241</t>
+          <t>463931</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>425241</t>
+          <t>463931</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>425241</t>
+          <t>463931</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6059,17 +6059,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>707452</t>
+          <t>773569</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>707452</t>
+          <t>773569</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>707452</t>
+          <t>773569</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6106,32 +6106,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>477261</t>
+          <t>263777</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>240232</t>
+          <t>226688</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1227438</t>
+          <t>307138</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>35,52%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6141,32 +6141,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>126318</t>
+          <t>144376</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>100023</t>
+          <t>121123</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>150946</t>
+          <t>169961</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6176,32 +6176,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>603580</t>
+          <t>408153</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>356457</t>
+          <t>364422</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1400988</t>
+          <t>459804</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>6,34%</t>
         </is>
       </c>
     </row>
@@ -6219,32 +6219,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>2978410</t>
+          <t>3264903</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2228233</t>
+          <t>3221542</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3215439</t>
+          <t>3301992</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>86,19%</t>
+          <t>92,52%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>64,48%</t>
+          <t>91,3%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>93,05%</t>
+          <t>93,58%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6254,32 +6254,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>3526216</t>
+          <t>3581184</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3501588</t>
+          <t>3555599</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3552511</t>
+          <t>3604437</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6289,32 +6289,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>6504624</t>
+          <t>6846087</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5707216</t>
+          <t>6794436</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6751747</t>
+          <t>6889818</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>91,51%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>80,29%</t>
+          <t>93,66%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>94,98%</t>
         </is>
       </c>
     </row>
@@ -6332,17 +6332,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3455671</t>
+          <t>3528680</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3455671</t>
+          <t>3528680</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3455671</t>
+          <t>3528680</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6367,17 +6367,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3652534</t>
+          <t>3725560</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3652534</t>
+          <t>3725560</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3652534</t>
+          <t>3725560</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6402,17 +6402,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7108204</t>
+          <t>7254240</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7108204</t>
+          <t>7254240</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7108204</t>
+          <t>7254240</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
